--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -5,102 +5,54 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRUEBASEXTRACTOR\Automatizacion\WhatsApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRUEBASEXTRACTOR\Automatizacion\WhatsApp\botvendedores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09CB019-6743-411B-AA8A-471D0BB5F8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BDDB5B-31BD-43D3-8479-135E0DFF7812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Vendedores" sheetId="1" r:id="rId1"/>
+    <sheet name="Vendedores" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>Código Vendedor</t>
-  </si>
-  <si>
-    <t>Nombre Vendedor</t>
-  </si>
-  <si>
-    <t>Teléfono</t>
-  </si>
-  <si>
-    <t>Clientes CALIF=D</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ABDEL MARTIN ARGOTT CARRASCO</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>ALIM GUZMAN</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>FERNANDO QUISPE TTITO</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>GRIZ KATHERINE LAGOS ESTRADA</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>GUISELL SOTOMAYOR SCHEREIBER</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>JURI</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>MARGGIORY ALMENDRA MEJIA CACERES</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>MARJORIE LUCERO YLLA FUENTES</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>MILAGROS EDITH SOLARES VARGAS</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>ROSA MARILUZ HUISA CONDORI</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>SHIRLE KATIUSKA CHOQUE FLORES</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
   <si>
     <t>WALTER CCOSCCO AYMA</t>
@@ -119,7 +71,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,36 +79,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F0F7"/>
-        <bgColor rgb="FFE7F0F7"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -171,12 +100,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,240 +403,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE86CED-79C6-4198-8C8C-911AFBD57A57}">
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1">
+        <v>970507377</v>
+      </c>
+      <c r="C1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2">
+        <v>986885522</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B3">
+        <v>946023348</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B4">
+        <v>970509997</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5">
+        <v>970599671</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2">
-        <v>970507377</v>
-      </c>
-      <c r="D3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B6">
+        <v>981347831</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7">
+        <v>970598573</v>
+      </c>
+      <c r="C7">
         <v>7</v>
       </c>
-      <c r="C4" s="2">
-        <v>986885522</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>981348575</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9">
+        <v>936092787</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2">
-        <v>946023348</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B10">
+        <v>908833364</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B11">
+        <v>994296675</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2">
-        <v>970509997</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B12">
+        <v>908833361</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B13">
+        <v>984938232</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2">
-        <v>970599671</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B14">
+        <v>981348717</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2">
-        <v>981347831</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="2">
-        <v>970598573</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2">
-        <v>981348575</v>
-      </c>
-      <c r="D10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2">
-        <v>936092787</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="2">
-        <v>908833364</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="2">
-        <v>994296675</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2">
-        <v>908833361</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2">
-        <v>984938232</v>
-      </c>
-      <c r="D15">
+      <c r="B15">
+        <v>940246472</v>
+      </c>
+      <c r="C15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>99</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="2">
-        <v>981348717</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>100</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="2">
-        <v>940246472</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRUEBASEXTRACTOR\Automatizacion\WhatsApp\botvendedores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BDDB5B-31BD-43D3-8479-135E0DFF7812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD145D1-42D0-4C6A-976A-BA1E95E28B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>ABDEL MARTIN ARGOTT CARRASCO</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>JEFE DE VENTAS</t>
-  </si>
-  <si>
-    <t>SUPERVISOR ARCOR</t>
   </si>
 </sst>
 </file>
@@ -404,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE86CED-79C6-4198-8C8C-911AFBD57A57}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
@@ -566,17 +563,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>940246472</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRUEBASEXTRACTOR\Automatizacion\WhatsApp\botvendedores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD145D1-42D0-4C6A-976A-BA1E95E28B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F88256-DF1C-42A4-877F-26FCBAACCC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>ABDEL MARTIN ARGOTT CARRASCO</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>JEFE DE VENTAS</t>
+  </si>
+  <si>
+    <t>VENDEDOR</t>
+  </si>
+  <si>
+    <t>ADMINISTRADOR</t>
   </si>
 </sst>
 </file>
@@ -401,15 +407,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE86CED-79C6-4198-8C8C-911AFBD57A57}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -419,8 +426,11 @@
       <c r="C1">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -430,8 +440,11 @@
       <c r="C2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -441,8 +454,11 @@
       <c r="C3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -452,8 +468,11 @@
       <c r="C4">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -463,8 +482,11 @@
       <c r="C5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -474,8 +496,11 @@
       <c r="C6">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -485,8 +510,11 @@
       <c r="C7">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -496,8 +524,11 @@
       <c r="C8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -507,8 +538,11 @@
       <c r="C9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -518,8 +552,11 @@
       <c r="C10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -529,8 +566,11 @@
       <c r="C11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -540,8 +580,11 @@
       <c r="C12">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -551,16 +594,22 @@
       <c r="C13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>981348717</v>
       </c>
       <c r="C14">
         <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRUEBASEXTRACTOR\Automatizacion\WhatsApp\botvendedores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F88256-DF1C-42A4-877F-26FCBAACCC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C110E9A-6839-44E0-8D0B-5A6570A47557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>ABDEL MARTIN ARGOTT CARRASCO</t>
   </si>
@@ -67,7 +67,19 @@
     <t>VENDEDOR</t>
   </si>
   <si>
-    <t>ADMINISTRADOR</t>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Clientes</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>OFICINA</t>
   </si>
 </sst>
 </file>
@@ -103,8 +115,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,208 +421,222 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE86CED-79C6-4198-8C8C-911AFBD57A57}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="1">
         <v>970507377</v>
       </c>
-      <c r="C1">
+      <c r="C2" s="1">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B3" s="1">
         <v>986885522</v>
       </c>
-      <c r="C2">
+      <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B4" s="1">
         <v>946023348</v>
       </c>
-      <c r="C3">
+      <c r="C4" s="1">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="1">
         <v>970509997</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="1">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B6" s="1">
         <v>970599671</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="1">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B7" s="1">
         <v>981347831</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="1">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B8" s="1">
         <v>970598573</v>
       </c>
-      <c r="C7">
+      <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="1">
         <v>981348575</v>
       </c>
-      <c r="C8">
+      <c r="C9" s="1">
         <v>11</v>
       </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B10" s="1">
         <v>936092787</v>
       </c>
-      <c r="C9">
+      <c r="C10" s="1">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B11" s="1">
         <v>908833364</v>
       </c>
-      <c r="C10">
+      <c r="C11" s="1">
         <v>7</v>
       </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B12" s="1">
         <v>994296675</v>
       </c>
-      <c r="C11">
+      <c r="C12" s="1">
         <v>9</v>
       </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B13" s="1">
         <v>908833361</v>
       </c>
-      <c r="C12">
+      <c r="C13" s="1">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B14" s="1">
         <v>984938232</v>
       </c>
-      <c r="C13">
+      <c r="C14" s="1">
         <v>0</v>
       </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
         <v>981348717</v>
       </c>
-      <c r="C14">
+      <c r="C15" s="1">
         <v>0</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" s="2" t="s">
         <v>13</v>
       </c>
     </row>

--- a/vendedores.xlsx
+++ b/vendedores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PRUEBASEXTRACTOR\Automatizacion\WhatsApp\botvendedores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C110E9A-6839-44E0-8D0B-5A6570A47557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEA517B-3DE0-4ED6-BF80-85429FE06438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t>ABDEL MARTIN ARGOTT CARRASCO</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Rol</t>
-  </si>
-  <si>
-    <t>OFICINA</t>
   </si>
 </sst>
 </file>
@@ -628,7 +625,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>981348717</v>
